--- a/context_DB/SOM_context_db.xlsx
+++ b/context_DB/SOM_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM64"/>
+  <dimension ref="A1:BN64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,65 +691,70 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt2</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt2</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE_evt2</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -866,7 +871,8 @@
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="n">
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -981,7 +987,8 @@
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="n">
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1002,7 +1009,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1096,7 +1103,8 @@
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="n">
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,7 +1125,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1211,7 +1219,8 @@
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="n">
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1318,16 +1327,16 @@
           <t>Woqooyi Galbeed</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>Hargeysa</t>
-        </is>
+      <c r="BA6" t="n">
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
         <v>2</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>SO12</t>
+        </is>
       </c>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr">
@@ -1352,21 +1361,26 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Police Forces of Somaliland (2024-) ---- Police Forces of Somaliland (2010-2024)</t>
+          <t>Police Forces of Somaliland (2010-2024) ---- Police Forces of Somaliland (2024-)</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>On 3 February 2025, parents and students of the Hargeysa university demonstrated in Hargeysa town (Hargeysa, Woqooyi Galbeed) against the increased tuition fees. The demonstrators damaged some of the educational materials and clashed with Somaliland police forces (means unspecified). ---- On 25 June 2024, a group of students pelted stones at the school building in Hargeysa town (Hargeysa, Woqooyi Galbeed) in a demonstration against the ongoing Somaliland national examinations. Somaliland police forces fired several shots in the air to disperse the group. Some parts of the premises were damaged during the incident.</t>
+          <t>On 25 June 2024, a group of students pelted stones at the school building in Hargeysa town (Hargeysa, Woqooyi Galbeed) in a demonstration against the ongoing Somaliland national examinations. Somaliland police forces fired several shots in the air to disperse the group. Some parts of the premises were damaged during the incident. ---- On 3 February 2025, parents and students of the Hargeysa university demonstrated in Hargeysa town (Hargeysa, Woqooyi Galbeed) against the increased tuition fees. The demonstrators damaged some of the educational materials and clashed with Somaliland police forces (means unspecified).</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>03 February 2025 ---- 25 June 2024</t>
-        </is>
-      </c>
-      <c r="BM6" t="n">
+          <t>2024-06-25 ---- 2025-02-03</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>Hargeysa</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1387,7 +1401,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1481,7 +1495,8 @@
       <c r="BJ7" t="inlineStr"/>
       <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="n">
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1588,16 +1603,16 @@
           <t>Woqooyi Galbeed</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>Gebiley</t>
-        </is>
+      <c r="BA8" t="n">
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>1</v>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>SO12</t>
+        </is>
       </c>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr">
@@ -1633,10 +1648,15 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>07 January 2025</t>
-        </is>
-      </c>
-      <c r="BM8" t="n">
+          <t>2025-01-07</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>Gebiley</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1751,7 +1771,8 @@
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="n">
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1858,16 +1879,16 @@
           <t>Togdheer</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>Buuhoodle</t>
-        </is>
+      <c r="BA10" t="n">
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
         <v>1</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>SO13</t>
+        </is>
       </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr">
@@ -1903,10 +1924,15 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>09 July 2024</t>
-        </is>
-      </c>
-      <c r="BM10" t="n">
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>Buuhoodle</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
         <v>0.6604534338026307</v>
       </c>
     </row>
@@ -1922,12 +1948,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SO2103</t>
+          <t>SO2403</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2021,7 +2047,8 @@
       <c r="BJ11" t="inlineStr"/>
       <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="n">
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2042,7 +2069,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2136,7 +2163,8 @@
       <c r="BJ12" t="inlineStr"/>
       <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="n">
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2157,7 +2185,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2251,7 +2279,8 @@
       <c r="BJ13" t="inlineStr"/>
       <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="n">
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="n">
         <v>0.2282372119268767</v>
       </c>
     </row>
@@ -2272,7 +2301,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2366,7 +2395,8 @@
       <c r="BJ14" t="inlineStr"/>
       <c r="BK14" t="inlineStr"/>
       <c r="BL14" t="inlineStr"/>
-      <c r="BM14" t="n">
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2387,7 +2417,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2481,7 +2511,8 @@
       <c r="BJ15" t="inlineStr"/>
       <c r="BK15" t="inlineStr"/>
       <c r="BL15" t="inlineStr"/>
-      <c r="BM15" t="n">
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="n">
         <v>0.2349906863447485</v>
       </c>
     </row>
@@ -2502,7 +2533,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2596,7 +2627,8 @@
       <c r="BJ16" t="inlineStr"/>
       <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="inlineStr"/>
-      <c r="BM16" t="n">
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="n">
         <v>0.2426554750095384</v>
       </c>
     </row>
@@ -2711,7 +2743,8 @@
       <c r="BJ17" t="inlineStr"/>
       <c r="BK17" t="inlineStr"/>
       <c r="BL17" t="inlineStr"/>
-      <c r="BM17" t="n">
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2727,12 +2760,12 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SO2606</t>
+          <t>SO2305</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2826,7 +2859,8 @@
       <c r="BJ18" t="inlineStr"/>
       <c r="BK18" t="inlineStr"/>
       <c r="BL18" t="inlineStr"/>
-      <c r="BM18" t="n">
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2941,7 +2975,8 @@
       <c r="BJ19" t="inlineStr"/>
       <c r="BK19" t="inlineStr"/>
       <c r="BL19" t="inlineStr"/>
-      <c r="BM19" t="n">
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="n">
         <v>0.04246723815154203</v>
       </c>
     </row>
@@ -2962,7 +2997,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3056,7 +3091,8 @@
       <c r="BJ20" t="inlineStr"/>
       <c r="BK20" t="inlineStr"/>
       <c r="BL20" t="inlineStr"/>
-      <c r="BM20" t="n">
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="n">
         <v>0.207718076843898</v>
       </c>
     </row>
@@ -3077,7 +3113,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SO1602;SO1702;SO1902;SO2501</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3171,7 +3207,8 @@
       <c r="BJ21" t="inlineStr"/>
       <c r="BK21" t="inlineStr"/>
       <c r="BL21" t="inlineStr"/>
-      <c r="BM21" t="n">
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3286,7 +3323,8 @@
       <c r="BJ22" t="inlineStr"/>
       <c r="BK22" t="inlineStr"/>
       <c r="BL22" t="inlineStr"/>
-      <c r="BM22" t="n">
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3401,7 +3439,8 @@
       <c r="BJ23" t="inlineStr"/>
       <c r="BK23" t="inlineStr"/>
       <c r="BL23" t="inlineStr"/>
-      <c r="BM23" t="n">
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3422,7 +3461,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3516,7 +3555,8 @@
       <c r="BJ24" t="inlineStr"/>
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
-      <c r="BM24" t="n">
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="n">
         <v>0.2590660057396295</v>
       </c>
     </row>
@@ -3631,7 +3671,8 @@
       <c r="BJ25" t="inlineStr"/>
       <c r="BK25" t="inlineStr"/>
       <c r="BL25" t="inlineStr"/>
-      <c r="BM25" t="n">
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="n">
         <v>0.3987382515771855</v>
       </c>
     </row>
@@ -3652,7 +3693,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SO1602;SO1702;SO1902;SO2501</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3746,7 +3787,8 @@
       <c r="BJ26" t="inlineStr"/>
       <c r="BK26" t="inlineStr"/>
       <c r="BL26" t="inlineStr"/>
-      <c r="BM26" t="n">
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3767,7 +3809,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SO1703;SO2003;SO2301;SO2102</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3861,7 +3903,8 @@
       <c r="BJ27" t="inlineStr"/>
       <c r="BK27" t="inlineStr"/>
       <c r="BL27" t="inlineStr"/>
-      <c r="BM27" t="n">
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3882,7 +3925,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3976,7 +4019,8 @@
       <c r="BJ28" t="inlineStr"/>
       <c r="BK28" t="inlineStr"/>
       <c r="BL28" t="inlineStr"/>
-      <c r="BM28" t="n">
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="n">
         <v>0.250577867227762</v>
       </c>
     </row>
@@ -3997,7 +4041,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4091,7 +4135,8 @@
       <c r="BJ29" t="inlineStr"/>
       <c r="BK29" t="inlineStr"/>
       <c r="BL29" t="inlineStr"/>
-      <c r="BM29" t="n">
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="n">
         <v>0.05927210589405494</v>
       </c>
     </row>
@@ -4112,7 +4157,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4206,7 +4251,8 @@
       <c r="BJ30" t="inlineStr"/>
       <c r="BK30" t="inlineStr"/>
       <c r="BL30" t="inlineStr"/>
-      <c r="BM30" t="n">
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="n">
         <v>0.007557292113224649</v>
       </c>
     </row>
@@ -4321,7 +4367,8 @@
       <c r="BJ31" t="inlineStr"/>
       <c r="BK31" t="inlineStr"/>
       <c r="BL31" t="inlineStr"/>
-      <c r="BM31" t="n">
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4342,7 +4389,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4428,16 +4475,16 @@
           <t>Galgaduud</t>
         </is>
       </c>
-      <c r="BA32" t="inlineStr">
-        <is>
-          <t>Dhuusamarreeb</t>
-        </is>
+      <c r="BA32" t="n">
+        <v>2</v>
       </c>
       <c r="BB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC32" t="n">
         <v>1</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>SO19</t>
+        </is>
       </c>
       <c r="BD32" t="inlineStr"/>
       <c r="BE32" t="inlineStr">
@@ -4473,10 +4520,15 @@
       </c>
       <c r="BL32" t="inlineStr">
         <is>
-          <t>23 June 2024</t>
-        </is>
-      </c>
-      <c r="BM32" t="n">
+          <t>2024-06-23</t>
+        </is>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>Dhuusamarreeb</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
         <v>0.1772293886707796</v>
       </c>
     </row>
@@ -4492,12 +4544,12 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SO2501</t>
+          <t>SO1601</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SO1602;SO1702;SO1902;SO2501</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4591,7 +4643,8 @@
       <c r="BJ33" t="inlineStr"/>
       <c r="BK33" t="inlineStr"/>
       <c r="BL33" t="inlineStr"/>
-      <c r="BM33" t="n">
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="n">
         <v>0.2060008032913234</v>
       </c>
     </row>
@@ -4612,7 +4665,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4706,7 +4759,8 @@
       <c r="BJ34" t="inlineStr"/>
       <c r="BK34" t="inlineStr"/>
       <c r="BL34" t="inlineStr"/>
-      <c r="BM34" t="n">
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="n">
         <v>0.0571134109159617</v>
       </c>
     </row>
@@ -4727,7 +4781,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4813,16 +4867,16 @@
           <t>Hiraan</t>
         </is>
       </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>Belet Weyne</t>
-        </is>
+      <c r="BA35" t="n">
+        <v>16</v>
       </c>
       <c r="BB35" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC35" t="n">
         <v>1</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>SO20</t>
+        </is>
       </c>
       <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr">
@@ -4858,10 +4912,15 @@
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>11 March 2025</t>
-        </is>
-      </c>
-      <c r="BM35" t="n">
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="BM35" t="inlineStr">
+        <is>
+          <t>Belet Weyne</t>
+        </is>
+      </c>
+      <c r="BN35" t="n">
         <v>0.2448316924908958</v>
       </c>
     </row>
@@ -4882,7 +4941,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4976,7 +5035,8 @@
       <c r="BJ36" t="inlineStr"/>
       <c r="BK36" t="inlineStr"/>
       <c r="BL36" t="inlineStr"/>
-      <c r="BM36" t="n">
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="n">
         <v>0.05997768882472603</v>
       </c>
     </row>
@@ -4997,7 +5057,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SO1703;SO2003;SO2301;SO2102</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -5091,7 +5151,8 @@
       <c r="BJ37" t="inlineStr"/>
       <c r="BK37" t="inlineStr"/>
       <c r="BL37" t="inlineStr"/>
-      <c r="BM37" t="n">
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="n">
         <v>0.3511450381679389</v>
       </c>
     </row>
@@ -5112,7 +5173,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5206,7 +5267,8 @@
       <c r="BJ38" t="inlineStr"/>
       <c r="BK38" t="inlineStr"/>
       <c r="BL38" t="inlineStr"/>
-      <c r="BM38" t="n">
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="n">
         <v>0.09863932614247056</v>
       </c>
     </row>
@@ -5227,7 +5289,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SO1703;SO2003;SO2301;SO2102</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5321,7 +5383,8 @@
       <c r="BJ39" t="inlineStr"/>
       <c r="BK39" t="inlineStr"/>
       <c r="BL39" t="inlineStr"/>
-      <c r="BM39" t="n">
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5342,7 +5405,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5428,55 +5491,60 @@
           <t>Middle Shabelle</t>
         </is>
       </c>
-      <c r="BA40" t="inlineStr">
-        <is>
-          <t>Balcad</t>
-        </is>
+      <c r="BA40" t="n">
+        <v>7</v>
       </c>
       <c r="BB40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>SO21</t>
+        </is>
       </c>
       <c r="BD40" t="inlineStr"/>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack ---- Attack ---- Attack</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>Abgal Clan Militia (Somalia)</t>
+          <t>Abgal Clan Militia (Somalia) ---- Unidentified Clan Militia (Somalia) ---- Abgal Abdalla-Galmaah Sub-Clan Militia (Somalia)</t>
         </is>
       </c>
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>Civilians (Somalia)</t>
+          <t>Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia)</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
         <is>
-          <t>Muslim Group (Somalia); Teachers (Somalia); Unidentified Clan Group (Somalia)</t>
+          <t>Muslim Group (Somalia); Teachers (Somalia); Unidentified Clan Group (Somalia) ---- Muslim Group (Somalia); Teachers (Somalia); Unidentified Clan Group (Somalia) ---- Abgal Clan Group (Somalia); Muslim Group (Somalia)</t>
         </is>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>On 3 January 2025, Abgal clan militia shot and killed two civilians including a prominent clan elder and a qur'anic teacher near Warshiikh village (Balcad, Middle Shabelle). The motive was due to clan dispute.</t>
+          <t>On 3 January 2025, Abgal clan militia shot and killed two civilians including a prominent clan elder and a qur'anic teacher near Warshiikh village (Balcad, Middle Shabelle). The motive was due to clan dispute. ---- On 29 May 2025, an unidentified clan militia shot and killed a civilian Quranic teacher in the vicinity of Warshiikh village (Balcad, Middle Shabelle). The motive was due to clan revenge. ---- On 12 June 2025, Abgal Abdalla-Galmaax sub-clan militia shot and killed 4 qur'anic teachers from Abgal clan in Xaloole village near Warshiikh village (Balcad, Middle Shabelle). The motive was due to clan revenge.</t>
         </is>
       </c>
       <c r="BL40" t="inlineStr">
         <is>
-          <t>03 January 2025</t>
-        </is>
-      </c>
-      <c r="BM40" t="n">
+          <t>2025-01-03 ---- 2025-05-29 ---- 2025-06-12</t>
+        </is>
+      </c>
+      <c r="BM40" t="inlineStr">
+        <is>
+          <t>Balcad</t>
+        </is>
+      </c>
+      <c r="BN40" t="n">
         <v>0.1179156594144507</v>
       </c>
     </row>
@@ -5497,7 +5565,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5591,7 +5659,8 @@
       <c r="BJ41" t="inlineStr"/>
       <c r="BK41" t="inlineStr"/>
       <c r="BL41" t="inlineStr"/>
-      <c r="BM41" t="n">
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5612,7 +5681,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5693,64 +5762,21 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>Banadir</t>
-        </is>
-      </c>
-      <c r="BA42" t="inlineStr">
-        <is>
-          <t>Banadir</t>
-        </is>
-      </c>
-      <c r="BB42" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>13</v>
-      </c>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
       <c r="BD42" t="inlineStr"/>
-      <c r="BE42" t="inlineStr">
-        <is>
-          <t>Explosions/Remote violence ---- Violence against civilians ---- Protests ---- Protests ---- Violence against civilians ---- Protests ---- Protests ---- Protests ---- Riots ---- Violence against civilians ---- Explosions/Remote violence ---- Protests ---- Battles</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>Shelling/artillery/missile attack ---- Abduction/forced disappearance ---- Peaceful protest ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Armed clash</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
-        <is>
-          <t>Al Shabaab ---- Al Shabaab ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Al Shabaab ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Rioters (Somalia) ---- Military Forces of Somalia (2022-) ---- Al Shabaab ---- Protesters (Somalia) ---- Al Shabaab</t>
-        </is>
-      </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>Students (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Students (Somalia) ---- Teachers (Somalia)</t>
-        </is>
-      </c>
-      <c r="BI42" t="inlineStr">
-        <is>
-          <t>Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Military Forces of Somalia (2022-)</t>
-        </is>
-      </c>
-      <c r="BJ42" t="inlineStr">
-        <is>
-          <t>Students (Somalia); Women (Somalia) ---- Teachers (Somalia) ---- Students (Somalia); Women (Somalia)</t>
-        </is>
-      </c>
-      <c r="BK42" t="inlineStr">
-        <is>
-          <t>On 5 April 2025, Al Shabaab fired 2 107mm rockets toward the Vila Somalia area, the mortars landing in civilian residence near 15 May School and in the vicinity of Daljirka Dahson near Villa Somalia in Mogadishu - Bondhere (Banadir). 1 mortar shell struck a civilian pharmacy, injuring 3 people and Al Shabaab claimed responsibility. ---- On 19 January 2025, suspected Al Shabaab kidnapped a female student from a school in the Zona K area in Mogadishu - Hodan (Afgooye, Lower Shabelle). The perpetrator used a Tuk-tuk, which a man and woman were already on board. The police arrived at the scene and tried to apprehend the suspect, but their efforts were unsuccessful. ---- On 9 December 2024, Banadir university students protested at the main gate of the university in Mogadishu - Hodan (Afgooye, Lower Shabelle) rejecting one year extension to their academic years. ---- On 21 November 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 26 October 2024, suspected Al Shabaab shot and killed a young boy and a teacher of the Al-Asaar rehabilitation center in Mogadishu - Dharkenley (Afgooye, Lower Shabelle). ---- On 23 September 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 19 September 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 14 July 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 24 June 2024, several students barricaded an unspecified road with burning tires and stones at the Gaheyr primary and secondary school in Mogadishu - Hamar Jabjab (Banadir) in a demonstration, demanding to be seated for the morning examination after they arrived late. ---- On 14 May 2024, government soldiers opened gunfire towards a minibus carrying passengers at the Ex Milk Factory roundabout near the Tarabunka junction neighborhood in Mogadishu - Hodan (Afgooye, Lower Shabelle). A stray bullet hit and killed a female university student. ---- On 10 March 2024, Al Shabaab fired several mortar shells that landed inside the Shibis Public School in Mogadishu - Shibis (Banadir). There were no fatalities. One civilian was injured. Al Shabaab claimed responsibility. ---- On 16 February 2024, family members, education association of Mogadishu, and teachers protested the recent killing of a teacher at his school in Mogadishu - Hodan (Banadir). The association has announced the closure of all universities and schools and suspended working for three days and demanded justice. ---- On 31 January 2024, overnight, Al Shabaab threw a hand grenade towards government soldiers (SNA) checkpoint near Mogadishu school in Mogadishu - Shibis (Banadir). The soldiers reacted with gunfire. One soldier was killed and another was injured. Al Shabaab claimed responsibility.</t>
-        </is>
-      </c>
-      <c r="BL42" t="inlineStr">
-        <is>
-          <t>05 April 2025 ---- 19 January 2025 ---- 09 December 2024 ---- 21 November 2024 ---- 26 October 2024 ---- 23 September 2024 ---- 19 September 2024 ---- 14 July 2024 ---- 24 June 2024 ---- 14 May 2024 ---- 10 March 2024 ---- 16 February 2024 ---- 31 January 2024</t>
-        </is>
-      </c>
-      <c r="BM42" t="n">
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="n">
         <v>0.774974545142581</v>
       </c>
     </row>
@@ -5771,7 +5797,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SO1703;SO2003;SO2301;SO2102</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5857,16 +5883,16 @@
           <t>Lower Shabelle</t>
         </is>
       </c>
-      <c r="BA43" t="inlineStr">
-        <is>
-          <t>Marka</t>
-        </is>
+      <c r="BA43" t="n">
+        <v>3</v>
       </c>
       <c r="BB43" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC43" t="n">
         <v>1</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>SO23</t>
+        </is>
       </c>
       <c r="BD43" t="inlineStr"/>
       <c r="BE43" t="inlineStr">
@@ -5902,10 +5928,15 @@
       </c>
       <c r="BL43" t="inlineStr">
         <is>
-          <t>17 July 2024</t>
-        </is>
-      </c>
-      <c r="BM43" t="n">
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="BM43" t="inlineStr">
+        <is>
+          <t>Marka</t>
+        </is>
+      </c>
+      <c r="BN43" t="n">
         <v>0.0697064546146688</v>
       </c>
     </row>
@@ -5926,7 +5957,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -6078,26 +6109,26 @@
           <t>Lower Shabelle</t>
         </is>
       </c>
-      <c r="BA44" t="inlineStr">
-        <is>
-          <t>Afgooye</t>
-        </is>
+      <c r="BA44" t="n">
+        <v>2</v>
       </c>
       <c r="BB44" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC44" t="n">
         <v>3</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>SO23</t>
+        </is>
       </c>
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Strategic developments ---- Violence against civilians</t>
+          <t>Violence against civilians ---- Strategic developments ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>Remote explosive/landmine/IED ---- Other ---- Abduction/forced disappearance</t>
+          <t>Abduction/forced disappearance ---- Other ---- Remote explosive/landmine/IED</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
@@ -6108,25 +6139,30 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Military Forces of Somalia (2022-) ---- Civilians (Somalia) ---- Civilians (Somalia)</t>
+          <t>Civilians (Somalia) ---- Civilians (Somalia) ---- Military Forces of Somalia (2022-)</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>Civilians (Somalia) ---- Labor Group (Somalia); Muslim Group (Somalia); Teachers (Somalia) ---- ASWJ: Ahlu Sunna Wal Jamaa; Muslim Group (Somalia)</t>
+          <t>ASWJ: Ahlu Sunna Wal Jamaa; Muslim Group (Somalia) ---- Labor Group (Somalia); Muslim Group (Somalia); Teachers (Somalia) ---- Civilians (Somalia)</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>On 2 December 2024, an IED planted by an unknown group (likely Al Shabaab, who carried out similar attacks and explosions in Mogadishu) inside a public restaurant, where SNA soldiers often gather for coffee, exploded at the Mira-Khat Market village, near the High School neighborhood in Afgooye town (Afgooye, Lower Shabelle). At least two people were killed, including one SNA soldier and a civilian bystander, while two others were injured in the blast. The explosion caused damage to the targeted restaurant. ---- Other: On 8 September 2024, several teachers from various schools, madrasa, and mosques Imams in Mogadishu traveled to an Al Shabaab-controlled area in Tawakal village (Afgooye, Lower Shabelle). The militants called all teachers and school management to attend Al-Shabaab training on curriculums. ---- On 7 June 2024, Al Shabaab abducted more than 30 Ahlu Sunna Wal Jamaa and quranic teachers members in Laantabuur village (Afgooye, Lower Shabelle). The member were attending preaching in session in the villages. The victims were take to Jilib-Marca.</t>
+          <t>On 7 June 2024, Al Shabaab abducted more than 30 Ahlu Sunna Wal Jamaa and quranic teachers members in Laantabuur village (Afgooye, Lower Shabelle). The member were attending preaching in session in the villages. The victims were take to Jilib-Marca. ---- Other: On 8 September 2024, several teachers from various schools, madrasa, and mosques Imams in Mogadishu traveled to an Al Shabaab-controlled area in Tawakal village (Afgooye, Lower Shabelle). The militants called all teachers and school management to attend Al-Shabaab training on curriculums. ---- On 2 December 2024, an IED planted by an unknown group (likely Al Shabaab, who carried out similar attacks and explosions in Mogadishu) inside a public restaurant, where SNA soldiers often gather for coffee, exploded at the Mira-Khat Market village, near the High School neighborhood in Afgooye town (Afgooye, Lower Shabelle). At least two people were killed, including one SNA soldier and a civilian bystander, while two others were injured in the blast. The explosion caused damage to the targeted restaurant.</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>02 December 2024 ---- 08 September 2024 ---- 07 June 2024</t>
-        </is>
-      </c>
-      <c r="BM44" t="n">
+          <t>2024-06-07 ---- 2024-09-08 ---- 2024-12-02</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>Afgooye</t>
+        </is>
+      </c>
+      <c r="BN44" t="n">
         <v>0.09919296044488904</v>
       </c>
     </row>
@@ -6147,7 +6183,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -6241,7 +6277,8 @@
       <c r="BJ45" t="inlineStr"/>
       <c r="BK45" t="inlineStr"/>
       <c r="BL45" t="inlineStr"/>
-      <c r="BM45" t="n">
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="n">
         <v>0.5852017937219731</v>
       </c>
     </row>
@@ -6262,7 +6299,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -6356,7 +6393,8 @@
       <c r="BJ46" t="inlineStr"/>
       <c r="BK46" t="inlineStr"/>
       <c r="BL46" t="inlineStr"/>
-      <c r="BM46" t="n">
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6377,7 +6415,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6471,7 +6509,8 @@
       <c r="BJ47" t="inlineStr"/>
       <c r="BK47" t="inlineStr"/>
       <c r="BL47" t="inlineStr"/>
-      <c r="BM47" t="n">
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="n">
         <v>0.007206942197381968</v>
       </c>
     </row>
@@ -6492,7 +6531,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -6586,7 +6625,8 @@
       <c r="BJ48" t="inlineStr"/>
       <c r="BK48" t="inlineStr"/>
       <c r="BL48" t="inlineStr"/>
-      <c r="BM48" t="n">
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="n">
         <v>0.6662489019033675</v>
       </c>
     </row>
@@ -6701,7 +6741,8 @@
       <c r="BJ49" t="inlineStr"/>
       <c r="BK49" t="inlineStr"/>
       <c r="BL49" t="inlineStr"/>
-      <c r="BM49" t="n">
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="n">
         <v>0.02155036538185987</v>
       </c>
     </row>
@@ -6722,7 +6763,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -6816,7 +6857,8 @@
       <c r="BJ50" t="inlineStr"/>
       <c r="BK50" t="inlineStr"/>
       <c r="BL50" t="inlineStr"/>
-      <c r="BM50" t="n">
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="n">
         <v>0.06797081325383213</v>
       </c>
     </row>
@@ -6837,7 +6879,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6931,7 +6973,8 @@
       <c r="BJ51" t="inlineStr"/>
       <c r="BK51" t="inlineStr"/>
       <c r="BL51" t="inlineStr"/>
-      <c r="BM51" t="n">
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="n">
         <v>0.4592630278363253</v>
       </c>
     </row>
@@ -6947,12 +6990,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SO1602</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SO1602;SO1702;SO1902;SO2501</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -7046,7 +7089,8 @@
       <c r="BJ52" t="inlineStr"/>
       <c r="BK52" t="inlineStr"/>
       <c r="BL52" t="inlineStr"/>
-      <c r="BM52" t="n">
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7067,7 +7111,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -7161,7 +7205,8 @@
       <c r="BJ53" t="inlineStr"/>
       <c r="BK53" t="inlineStr"/>
       <c r="BL53" t="inlineStr"/>
-      <c r="BM53" t="n">
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="n">
         <v>0.692101226993865</v>
       </c>
     </row>
@@ -7276,7 +7321,8 @@
       <c r="BJ54" t="inlineStr"/>
       <c r="BK54" t="inlineStr"/>
       <c r="BL54" t="inlineStr"/>
-      <c r="BM54" t="n">
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="n">
         <v>0.2460812539987204</v>
       </c>
     </row>
@@ -7297,7 +7343,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7391,7 +7437,8 @@
       <c r="BJ55" t="inlineStr"/>
       <c r="BK55" t="inlineStr"/>
       <c r="BL55" t="inlineStr"/>
-      <c r="BM55" t="n">
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="n">
         <v>0.09478334034497266</v>
       </c>
     </row>
@@ -7412,7 +7459,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -7506,7 +7553,8 @@
       <c r="BJ56" t="inlineStr"/>
       <c r="BK56" t="inlineStr"/>
       <c r="BL56" t="inlineStr"/>
-      <c r="BM56" t="n">
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="n">
         <v>0.5462396107845124</v>
       </c>
     </row>
@@ -7527,7 +7575,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -7621,7 +7669,8 @@
       <c r="BJ57" t="inlineStr"/>
       <c r="BK57" t="inlineStr"/>
       <c r="BL57" t="inlineStr"/>
-      <c r="BM57" t="n">
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="n">
         <v>0.3353127879594553</v>
       </c>
     </row>
@@ -7642,7 +7691,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -7736,7 +7785,8 @@
       <c r="BJ58" t="inlineStr"/>
       <c r="BK58" t="inlineStr"/>
       <c r="BL58" t="inlineStr"/>
-      <c r="BM58" t="n">
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="n">
         <v>0.1123930391308528</v>
       </c>
     </row>
@@ -7757,7 +7807,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -7851,7 +7901,8 @@
       <c r="BJ59" t="inlineStr"/>
       <c r="BK59" t="inlineStr"/>
       <c r="BL59" t="inlineStr"/>
-      <c r="BM59" t="n">
+      <c r="BM59" t="inlineStr"/>
+      <c r="BN59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7867,12 +7918,12 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SO1502</t>
+          <t>SO2104</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7966,7 +8017,8 @@
       <c r="BJ60" t="inlineStr"/>
       <c r="BK60" t="inlineStr"/>
       <c r="BL60" t="inlineStr"/>
-      <c r="BM60" t="n">
+      <c r="BM60" t="inlineStr"/>
+      <c r="BN60" t="n">
         <v>0.4475268781134164</v>
       </c>
     </row>
@@ -7987,7 +8039,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -8073,51 +8125,64 @@
           <t>Lower Juba</t>
         </is>
       </c>
-      <c r="BA61" t="inlineStr">
-        <is>
-          <t>Kismaayo</t>
-        </is>
+      <c r="BA61" t="n">
+        <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>SO28</t>
+        </is>
       </c>
       <c r="BD61" t="inlineStr"/>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>Strategic developments</t>
+          <t>Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other ---- Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>Military Forces of Somalia (2022-) Jubaland Intelligence and Security Agency</t>
-        </is>
-      </c>
-      <c r="BH61" t="inlineStr"/>
+          <t>Military Forces of Somalia (2022-) Jubaland Intelligence and Security Agency ---- Gaaljecel Clan Militia (Somalia)</t>
+        </is>
+      </c>
+      <c r="BH61" t="inlineStr">
+        <is>
+          <t>Tuni Clan Militia (Somalia)</t>
+        </is>
+      </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>Al Shabaab</t>
-        </is>
-      </c>
-      <c r="BJ61" t="inlineStr"/>
+          <t>Al Shabaab ---- Civilians (Somalia)</t>
+        </is>
+      </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>Abdalle Clan Group (Somalia); Women (Somalia)</t>
+        </is>
+      </c>
       <c r="BK61" t="inlineStr">
         <is>
-          <t>Other: On 4 March 2025, Jubaland Intelligence and Security Agency (JISA) arrested an Al Shabaab operative who was both a primary school teacher and a university student in Kismayo town (Kismaayo, Lower Juba). The militant revealed plans for abductions in town and attacks on the KDF seaport base and confirmed the existence of another Al Shabaab team, including suicide attackers, targeting government installations and public centers.</t>
+          <t>Other: On 4 March 2025, Jubaland Intelligence and Security Agency (JISA) arrested an Al Shabaab operative who was both a primary school teacher and a university student in Kismayo town (Kismaayo, Lower Juba). The militant revealed plans for abductions in town and attacks on the KDF seaport base and confirmed the existence of another Al Shabaab team, including suicide attackers, targeting government installations and public centers. ---- Around 14 July 2025 (as reported), two youths from Gaaljacel and Tuni clan militias abducted a young girl from the Abdalle clan from the Ahmed Gurey school in Midnimo village in Kismayo town (Kismaayo, Lower Juba). The girls were rescued by local police after five days. During an agreement between the Gaaljacel and Tuni and Abdalle after the incident, the Gaaljacel and Tuni clans paid an unspecified amount of money to the Abdalle clan as compensation for the sexual harassment.</t>
         </is>
       </c>
       <c r="BL61" t="inlineStr">
         <is>
-          <t>04 March 2025</t>
-        </is>
-      </c>
-      <c r="BM61" t="n">
+          <t>2025-03-04 ---- 2025-07-14</t>
+        </is>
+      </c>
+      <c r="BM61" t="inlineStr">
+        <is>
+          <t>Kismaayo</t>
+        </is>
+      </c>
+      <c r="BN61" t="n">
         <v>0.3314653835237586</v>
       </c>
     </row>
@@ -8138,7 +8203,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -8224,16 +8289,16 @@
           <t>Lower Juba</t>
         </is>
       </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>Afmadow</t>
-        </is>
+      <c r="BA62" t="n">
+        <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC62" t="n">
         <v>1</v>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>SO28</t>
+        </is>
       </c>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr">
@@ -8269,10 +8334,15 @@
       </c>
       <c r="BL62" t="inlineStr">
         <is>
-          <t>24 May 2024</t>
-        </is>
-      </c>
-      <c r="BM62" t="n">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="BM62" t="inlineStr">
+        <is>
+          <t>Afmadow</t>
+        </is>
+      </c>
+      <c r="BN62" t="n">
         <v>0.1797447056904707</v>
       </c>
     </row>
@@ -8293,7 +8363,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -8374,20 +8444,65 @@
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr"/>
       <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr"/>
-      <c r="BA63" t="inlineStr"/>
-      <c r="BB63" t="inlineStr"/>
-      <c r="BC63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>Lower Juba</t>
+        </is>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>SO28</t>
+        </is>
+      </c>
       <c r="BD63" t="inlineStr"/>
-      <c r="BE63" t="inlineStr"/>
-      <c r="BF63" t="inlineStr"/>
-      <c r="BG63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>Al Shabaab</t>
+        </is>
+      </c>
       <c r="BH63" t="inlineStr"/>
-      <c r="BI63" t="inlineStr"/>
-      <c r="BJ63" t="inlineStr"/>
-      <c r="BK63" t="inlineStr"/>
-      <c r="BL63" t="inlineStr"/>
-      <c r="BM63" t="n">
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>Civilians (Somalia)</t>
+        </is>
+      </c>
+      <c r="BJ63" t="inlineStr">
+        <is>
+          <t>Teachers (Somalia)</t>
+        </is>
+      </c>
+      <c r="BK63" t="inlineStr">
+        <is>
+          <t>On 31 May 2025, Al Shabaab abducted six young men from Badhaadhe town (Badhaadhe, Lower Juba) and transferred them to Jilib, where they were subjected to physical and psychological abuse under coercion to confess to alleged affiliations with government forces. Among the detainees is a schoolteacher from Kulbiyow village, who was apprehended while traveling from Kismayo.</t>
+        </is>
+      </c>
+      <c r="BL63" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="BM63" t="inlineStr">
+        <is>
+          <t>Badhaadhe</t>
+        </is>
+      </c>
+      <c r="BN63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8408,7 +8523,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1202;SO1303;SO1304;SO1401;SO1402;SO1403;SO1404;SO1502;SO1601;SO1606;SO1801;SO1802;SO1803;SO1901;SO1903;SO2001;SO2002;SO2101;SO2103;SO2104;SO2201;SO2302;SO2303;SO2305;SO2307;SO2401;SO2403;SO2404;SO2502;SO2601;SO2602;SO2603;SO2604;SO2605;SO2606;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -8494,16 +8609,16 @@
           <t>Lower Juba</t>
         </is>
       </c>
-      <c r="BA64" t="inlineStr">
-        <is>
-          <t>Jamaame</t>
-        </is>
+      <c r="BA64" t="n">
+        <v>0</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC64" t="n">
         <v>1</v>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>SO28</t>
+        </is>
       </c>
       <c r="BD64" t="inlineStr"/>
       <c r="BE64" t="inlineStr">
@@ -8535,10 +8650,15 @@
       </c>
       <c r="BL64" t="inlineStr">
         <is>
-          <t>18 March 2024</t>
-        </is>
-      </c>
-      <c r="BM64" t="n">
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="BM64" t="inlineStr">
+        <is>
+          <t>Jamaame</t>
+        </is>
+      </c>
+      <c r="BN64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8548,10 +8668,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -8563,13 +8683,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -8578,7 +8700,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -8596,52 +8718,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -8669,6 +8796,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -8782,21 +8920,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E66E496D-6DE2-448B-9BE4-1DAA9DFF962D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B8869E-561B-4D7B-B5CF-663EEBECC15F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{088BCADF-81F5-4020-8F67-309D6F22E71B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BFDFA4-5A80-458D-A2FE-FA44B5F171B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{994CA6B2-3662-4DFF-9381-D0E8AE6517A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21CFC321-ADC6-466C-AA54-D23B7F6A64AF}"/>
 </file>
--- a/context_DB/SOM_context_db.xlsx
+++ b/context_DB/SOM_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN64"/>
+  <dimension ref="A1:BN66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5783,74 +5783,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SO2301</t>
+          <t>SO2213</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SO2003</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I43" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>140.09</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -5880,70 +5838,74 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>Lower Shabelle</t>
+          <t>Banadir</t>
         </is>
       </c>
       <c r="BA43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB43" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>SO23</t>
+          <t>SO22</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr"/>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Battles ---- Protests ---- Explosions/Remote violence ---- Violence against civilians ---- Riots ---- Protests ---- Protests ---- Protests ---- Violence against civilians ---- Protests ---- Protests ---- Violence against civilians ---- Explosions/Remote violence ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Armed clash ---- Peaceful protest ---- Shelling/artillery/missile attack ---- Attack ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Attack ---- Peaceful protest ---- Peaceful protest ---- Abduction/forced disappearance ---- Shelling/artillery/missile attack ---- Attack</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>ATMIS: African Union Transition Mission in Somalia (2022-2024) (Uganda)</t>
-        </is>
-      </c>
-      <c r="BH43" t="inlineStr"/>
+          <t>Al Shabaab ---- Protesters (Somalia) ---- Al Shabaab ---- Military Forces of Somalia (2022-) ---- Rioters (Somalia) ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Al Shabaab ---- Protesters (Somalia) ---- Protesters (Somalia) ---- Al Shabaab ---- Al Shabaab ---- Al Shabaab</t>
+        </is>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>Teachers (Somalia) ---- Students (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Teachers (Somalia) ---- Students (Somalia)</t>
+        </is>
+      </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Civilians (Somalia)</t>
+          <t>Military Forces of Somalia (2022-) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia) ---- Civilians (Somalia)</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>Farmers (Somalia)</t>
+          <t>Students (Somalia); Women (Somalia) ---- Teachers (Somalia) ---- Students (Somalia); Women (Somalia) ---- Teachers (Somalia)</t>
         </is>
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>On 17 July 2024, ATMIS UPDF shot and killed three farmers, including an underage schoolboy, and injured another on their farm in Bulo Mareer town (Marka, Lower Shabelle). There is no further information.</t>
+          <t>On 31 January 2024, overnight, Al Shabaab threw a hand grenade towards government soldiers (SNA) checkpoint near Mogadishu school in Mogadishu - Shibis (Banadir). The soldiers reacted with gunfire. One soldier was killed and another was injured. Al Shabaab claimed responsibility. ---- On 16 February 2024, family members, education association of Mogadishu, and teachers protested the recent killing of a teacher at his school in Mogadishu - Hodan (Banadir). The association has announced the closure of all universities and schools and suspended working for three days and demanded justice. ---- On 10 March 2024, Al Shabaab fired several mortar shells that landed inside the Shibis Public School in Mogadishu - Shibis (Banadir). There were no fatalities. One civilian was injured. Al Shabaab claimed responsibility. ---- On 14 May 2024, government soldiers opened gunfire towards a minibus carrying passengers at the Ex Milk Factory roundabout near the Tarabunka junction neighborhood in Mogadishu - Hodan (Afgooye, Lower Shabelle). A stray bullet hit and killed a female university student. ---- On 24 June 2024, several students barricaded an unspecified road with burning tires and stones at the Gaheyr primary and secondary school in Mogadishu - Hamar Jabjab (Banadir) in a demonstration, demanding to be seated for the morning examination after they arrived late. ---- On 14 July 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 19 September 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 23 September 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 26 October 2024, suspected Al Shabaab shot and killed a young boy and a teacher of the Al-Asaar rehabilitation center in Mogadishu - Dharkenley (Afgooye, Lower Shabelle). ---- On 21 November 2024, a group of teachers protested in front of the Ministry of Education, Culture, and Higher Education, in Mogadishu - Hodan (Afgooye, Lower Shabelle) against their dismissal from government schools and claimed that the government replaced them with other teachers. ---- On 9 December 2024, Banadir university students protested at the main gate of the university in Mogadishu - Hodan (Afgooye, Lower Shabelle) rejecting one year extension to their academic years. ---- On 19 January 2025, suspected Al Shabaab kidnapped a female student from a school in the Zona K area in Mogadishu - Hodan (Afgooye, Lower Shabelle). The perpetrator used a Tuk-tuk, which a man and woman were already on board. The police arrived at the scene and tried to apprehend the suspect, but their efforts were unsuccessful. ---- On 5 April 2025, Al Shabaab fired 2 107mm rockets toward the Vila Somalia area, the mortars landing in civilian residence near 15 May School and in the vicinity of Daljirka Dahson near Villa Somalia in Mogadishu - Bondhere (Banadir). 1 mortar shell struck a civilian pharmacy, injuring 3 people and Al Shabaab claimed responsibility. ---- On 28 June 2025, Al Shabaab shot and killed a teacher at Yaaqshid School in Mogadishu - Yaqshid (Banadir). The motive for the killing remains unknown.</t>
         </is>
       </c>
       <c r="BL43" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-01-31 ---- 2024-02-16 ---- 2024-03-10 ---- 2024-05-14 ---- 2024-06-24 ---- 2024-07-14 ---- 2024-09-19 ---- 2024-09-23 ---- 2024-10-26 ---- 2024-11-21 ---- 2024-12-09 ---- 2025-01-19 ---- 2025-04-05 ---- 2025-06-28</t>
         </is>
       </c>
       <c r="BM43" t="inlineStr">
         <is>
-          <t>Marka</t>
+          <t>Banadir</t>
         </is>
       </c>
       <c r="BN43" t="n">
-        <v>0.0697064546146688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO2301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -5952,34 +5914,34 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SO1606</t>
+          <t>SO2003</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1602;SO1702;SO1703;SO2003;SO2301;SO2102</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>11.8</v>
+        <v>48.8</v>
       </c>
       <c r="I44" t="n">
-        <v>80</v>
+        <v>51.2</v>
       </c>
       <c r="J44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>88.2</v>
+        <v>51.2</v>
       </c>
       <c r="M44" t="n">
-        <v>157.1</v>
+        <v>140.09</v>
       </c>
       <c r="N44" t="n">
-        <v>5.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6006,103 +5968,37 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>7.800000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
-      <c r="Y44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> January 2025: A student was kidnapped from an education facility by suspected Al-Shabaab militants using a tuk-tuk.</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr">
-        <is>
-          <t>Al-Shabaab</t>
-        </is>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No Information on the Weapon Used</t>
-        </is>
-      </c>
-      <c r="AV44" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
       <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>NoInformation</t>
-        </is>
-      </c>
+      <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
@@ -6110,10 +6006,10 @@
         </is>
       </c>
       <c r="BA44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
@@ -6123,53 +6019,53 @@
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Strategic developments ---- Explosions/Remote violence</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance ---- Other ---- Remote explosive/landmine/IED</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>Al Shabaab ---- Al Shabaab ---- Al Shabaab</t>
+          <t>ATMIS: African Union Transition Mission in Somalia (2022-2024) (Uganda)</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Civilians (Somalia) ---- Civilians (Somalia) ---- Military Forces of Somalia (2022-)</t>
+          <t>Civilians (Somalia)</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
         <is>
-          <t>ASWJ: Ahlu Sunna Wal Jamaa; Muslim Group (Somalia) ---- Labor Group (Somalia); Muslim Group (Somalia); Teachers (Somalia) ---- Civilians (Somalia)</t>
+          <t>Farmers (Somalia)</t>
         </is>
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>On 7 June 2024, Al Shabaab abducted more than 30 Ahlu Sunna Wal Jamaa and quranic teachers members in Laantabuur village (Afgooye, Lower Shabelle). The member were attending preaching in session in the villages. The victims were take to Jilib-Marca. ---- Other: On 8 September 2024, several teachers from various schools, madrasa, and mosques Imams in Mogadishu traveled to an Al Shabaab-controlled area in Tawakal village (Afgooye, Lower Shabelle). The militants called all teachers and school management to attend Al-Shabaab training on curriculums. ---- On 2 December 2024, an IED planted by an unknown group (likely Al Shabaab, who carried out similar attacks and explosions in Mogadishu) inside a public restaurant, where SNA soldiers often gather for coffee, exploded at the Mira-Khat Market village, near the High School neighborhood in Afgooye town (Afgooye, Lower Shabelle). At least two people were killed, including one SNA soldier and a civilian bystander, while two others were injured in the blast. The explosion caused damage to the targeted restaurant.</t>
+          <t>On 17 July 2024, ATMIS UPDF shot and killed three farmers, including an underage schoolboy, and injured another on their farm in Bulo Mareer town (Marka, Lower Shabelle). There is no further information.</t>
         </is>
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>2024-06-07 ---- 2024-09-08 ---- 2024-12-02</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="BM44" t="inlineStr">
         <is>
-          <t>Afgooye</t>
+          <t>Marka</t>
         </is>
       </c>
       <c r="BN44" t="n">
-        <v>0.09919296044488904</v>
+        <v>0.0697064546146688</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SO2303</t>
+          <t>SO2302</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -6178,43 +6074,43 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SO1304</t>
+          <t>SO1606</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>66</v>
+        <v>11.8</v>
       </c>
       <c r="I45" t="n">
-        <v>28.6</v>
+        <v>80</v>
       </c>
       <c r="J45" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="L45" t="n">
-        <v>34</v>
+        <v>88.2</v>
       </c>
       <c r="M45" t="n">
-        <v>43.86</v>
+        <v>157.1</v>
       </c>
       <c r="N45" t="n">
-        <v>7.61</v>
+        <v>5.470000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6232,60 +6128,170 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="X45" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> January 2025: A student was kidnapped from an education facility by suspected Al-Shabaab militants using a tuk-tuk.</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>Al-Shabaab</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No Information on the Weapon Used</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
       <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>NoInformation</t>
+        </is>
+      </c>
       <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>Lower Shabelle</t>
+        </is>
+      </c>
+      <c r="BA45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>SO23</t>
+        </is>
+      </c>
       <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
-      <c r="BG45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Strategic developments ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance ---- Other ---- Remote explosive/landmine/IED</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>Al Shabaab ---- Al Shabaab ---- Al Shabaab</t>
+        </is>
+      </c>
       <c r="BH45" t="inlineStr"/>
-      <c r="BI45" t="inlineStr"/>
-      <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="inlineStr"/>
-      <c r="BL45" t="inlineStr"/>
-      <c r="BM45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>Civilians (Somalia) ---- Civilians (Somalia) ---- Military Forces of Somalia (2022-)</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>ASWJ: Ahlu Sunna Wal Jamaa; Muslim Group (Somalia) ---- Labor Group (Somalia); Muslim Group (Somalia); Teachers (Somalia) ---- Civilians (Somalia)</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>On 7 June 2024, Al Shabaab abducted more than 30 Ahlu Sunna Wal Jamaa and quranic teachers members in Laantabuur village (Afgooye, Lower Shabelle). The member were attending preaching in session in the villages. The victims were take to Jilib-Marca. ---- Other: On 8 September 2024, several teachers from various schools, madrasa, and mosques Imams in Mogadishu traveled to an Al Shabaab-controlled area in Tawakal village (Afgooye, Lower Shabelle). The militants called all teachers and school management to attend Al-Shabaab training on curriculums. ---- On 2 December 2024, an IED planted by an unknown group (likely Al Shabaab, who carried out similar attacks and explosions in Mogadishu) inside a public restaurant, where SNA soldiers often gather for coffee, exploded at the Mira-Khat Market village, near the High School neighborhood in Afgooye town (Afgooye, Lower Shabelle). At least two people were killed, including one SNA soldier and a civilian bystander, while two others were injured in the blast. The explosion caused damage to the targeted restaurant.</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>2024-06-07 ---- 2024-09-08 ---- 2024-12-02</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>Afgooye</t>
+        </is>
+      </c>
       <c r="BN45" t="n">
-        <v>0.5852017937219731</v>
+        <v>0.09919296044488904</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SO2305</t>
+          <t>SO2303</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -6294,43 +6300,43 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SO1502</t>
+          <t>SO1304</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>36.9</v>
+        <v>66</v>
       </c>
       <c r="I46" t="n">
-        <v>60.2</v>
+        <v>28.6</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="K46" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" t="n">
-        <v>63.1</v>
+        <v>34</v>
       </c>
       <c r="M46" t="n">
-        <v>58.92</v>
+        <v>43.86</v>
       </c>
       <c r="N46" t="n">
-        <v>0.41</v>
+        <v>7.61</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.41</v>
+        <v>1.06</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -6348,10 +6354,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
@@ -6395,13 +6401,13 @@
       <c r="BL46" t="inlineStr"/>
       <c r="BM46" t="inlineStr"/>
       <c r="BN46" t="n">
-        <v>0</v>
+        <v>0.5852017937219731</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SO2307</t>
+          <t>SO2305</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -6410,43 +6416,43 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO1502</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>48.7</v>
+        <v>36.9</v>
       </c>
       <c r="I47" t="n">
-        <v>48.5</v>
+        <v>60.2</v>
       </c>
       <c r="J47" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K47" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="L47" t="n">
-        <v>51.3</v>
+        <v>63.1</v>
       </c>
       <c r="M47" t="n">
-        <v>64.74000000000001</v>
+        <v>58.92</v>
       </c>
       <c r="N47" t="n">
-        <v>28.99</v>
+        <v>0.41</v>
       </c>
       <c r="O47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6455,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -6464,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3.44</v>
+        <v>2.07</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -6511,13 +6517,13 @@
       <c r="BL47" t="inlineStr"/>
       <c r="BM47" t="inlineStr"/>
       <c r="BN47" t="n">
-        <v>0.007206942197381968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SO2401</t>
+          <t>SO2307</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -6526,40 +6532,40 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO2602</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>55.7</v>
+        <v>48.7</v>
       </c>
       <c r="I48" t="n">
-        <v>33.8</v>
+        <v>48.5</v>
       </c>
       <c r="J48" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="L48" t="n">
-        <v>44.3</v>
+        <v>51.3</v>
       </c>
       <c r="M48" t="n">
-        <v>54.23</v>
+        <v>64.74000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>13.25</v>
+        <v>28.99</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P48" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -6571,19 +6577,19 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0.41</v>
+        <v>0.65</v>
       </c>
       <c r="U48" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3.01</v>
+        <v>3.44</v>
       </c>
       <c r="X48" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
@@ -6627,13 +6633,13 @@
       <c r="BL48" t="inlineStr"/>
       <c r="BM48" t="inlineStr"/>
       <c r="BN48" t="n">
-        <v>0.6662489019033675</v>
+        <v>0.007206942197381968</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SO2402</t>
+          <t>SO2401</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -6642,40 +6648,40 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SO1603</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SO1101;SO1102;SO1201;SO1203;SO1301;SO1302;SO1501;SO1503;SO1603;SO1604;SO1701;SO1804;SO2402;SO2504</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4.2</v>
+        <v>55.7</v>
       </c>
       <c r="I49" t="n">
-        <v>86.7</v>
+        <v>33.8</v>
       </c>
       <c r="J49" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>95.8</v>
+        <v>44.3</v>
       </c>
       <c r="M49" t="n">
-        <v>182.45</v>
+        <v>54.23</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>13.25</v>
       </c>
       <c r="O49" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>11.38</v>
+        <v>0.41</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -6687,19 +6693,19 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
@@ -6743,13 +6749,13 @@
       <c r="BL49" t="inlineStr"/>
       <c r="BM49" t="inlineStr"/>
       <c r="BN49" t="n">
-        <v>0.02155036538185987</v>
+        <v>0.6662489019033675</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SO2403</t>
+          <t>SO2402</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -6758,43 +6764,43 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SO1303</t>
+          <t>SO1603</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1101;SO1102;SO1201;SO1203;SO1301;SO1302;SO1501;SO1503;SO1603;SO1604;SO1701;SO1804;SO2402;SO2504</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>44.7</v>
+        <v>4.2</v>
       </c>
       <c r="I50" t="n">
-        <v>37.1</v>
+        <v>86.7</v>
       </c>
       <c r="J50" t="n">
-        <v>17.6</v>
+        <v>9.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>55.3</v>
+        <v>95.8</v>
       </c>
       <c r="M50" t="n">
-        <v>67.72</v>
+        <v>182.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="P50" t="n">
-        <v>14.53</v>
+        <v>11.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>22.75</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -6812,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -6859,13 +6865,13 @@
       <c r="BL50" t="inlineStr"/>
       <c r="BM50" t="inlineStr"/>
       <c r="BN50" t="n">
-        <v>0.06797081325383213</v>
+        <v>0.02155036538185987</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SO2404</t>
+          <t>SO2403</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -6874,7 +6880,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO1303</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -6883,40 +6889,40 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>40.2</v>
+        <v>44.7</v>
       </c>
       <c r="I51" t="n">
-        <v>21.7</v>
+        <v>37.1</v>
       </c>
       <c r="J51" t="n">
-        <v>34.2</v>
+        <v>17.6</v>
       </c>
       <c r="K51" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="L51" t="n">
-        <v>59.8</v>
+        <v>55.3</v>
       </c>
       <c r="M51" t="n">
-        <v>43.43</v>
+        <v>67.72</v>
       </c>
       <c r="N51" t="n">
-        <v>70.38</v>
+        <v>0.51</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="P51" t="n">
-        <v>0.72</v>
+        <v>14.53</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -6928,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>7.83</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -6975,13 +6981,13 @@
       <c r="BL51" t="inlineStr"/>
       <c r="BM51" t="inlineStr"/>
       <c r="BN51" t="n">
-        <v>0.4592630278363253</v>
+        <v>0.06797081325383213</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SO2501</t>
+          <t>SO2404</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -6990,7 +6996,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SO2101</t>
+          <t>SO2604</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6999,40 +7005,40 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>48.6</v>
+        <v>40.2</v>
       </c>
       <c r="I52" t="n">
-        <v>47.7</v>
+        <v>21.7</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>34.2</v>
       </c>
       <c r="K52" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L52" t="n">
-        <v>51.4</v>
+        <v>59.8</v>
       </c>
       <c r="M52" t="n">
-        <v>43.12</v>
+        <v>43.43</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>70.38</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -7044,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3.67</v>
+        <v>7.83</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -7091,13 +7097,13 @@
       <c r="BL52" t="inlineStr"/>
       <c r="BM52" t="inlineStr"/>
       <c r="BN52" t="n">
-        <v>0</v>
+        <v>0.4592630278363253</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SO2502</t>
+          <t>SO2501</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -7106,7 +7112,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SO2801</t>
+          <t>SO2101</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7115,55 +7121,55 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>26.5</v>
+        <v>48.6</v>
       </c>
       <c r="I53" t="n">
-        <v>50</v>
+        <v>47.7</v>
       </c>
       <c r="J53" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="L53" t="n">
-        <v>73.5</v>
+        <v>51.4</v>
       </c>
       <c r="M53" t="n">
-        <v>109.33</v>
+        <v>43.12</v>
       </c>
       <c r="N53" t="n">
-        <v>9.289999999999999</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>6.44</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>8.85</v>
+        <v>3.67</v>
       </c>
       <c r="X53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
@@ -7207,13 +7213,13 @@
       <c r="BL53" t="inlineStr"/>
       <c r="BM53" t="inlineStr"/>
       <c r="BN53" t="n">
-        <v>0.692101226993865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SO2504</t>
+          <t>SO2502</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -7222,64 +7228,64 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SO1503</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SO1101;SO1102;SO1201;SO1203;SO1301;SO1302;SO1501;SO1503;SO1603;SO1604;SO1701;SO1804;SO2402;SO2504</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>71.09999999999999</v>
+        <v>26.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28.4</v>
+        <v>50</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4</v>
+        <v>18.3</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L54" t="n">
-        <v>28.9</v>
+        <v>73.5</v>
       </c>
       <c r="M54" t="n">
-        <v>58.5</v>
+        <v>109.33</v>
       </c>
       <c r="N54" t="n">
-        <v>0.43</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P54" t="n">
-        <v>1.29</v>
+        <v>6.44</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
@@ -7323,13 +7329,13 @@
       <c r="BL54" t="inlineStr"/>
       <c r="BM54" t="inlineStr"/>
       <c r="BN54" t="n">
-        <v>0.2460812539987204</v>
+        <v>0.692101226993865</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SO2601</t>
+          <t>SO2504</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -7338,40 +7344,40 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO1503</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1101;SO1102;SO1201;SO1203;SO1301;SO1302;SO1501;SO1503;SO1603;SO1604;SO1701;SO1804;SO2402;SO2504</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>71.2</v>
+        <v>28.4</v>
       </c>
       <c r="J55" t="n">
-        <v>12.8</v>
+        <v>0.4</v>
       </c>
       <c r="K55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>86.3</v>
+        <v>28.9</v>
       </c>
       <c r="M55" t="n">
-        <v>124.44</v>
+        <v>58.5</v>
       </c>
       <c r="N55" t="n">
-        <v>28.75</v>
+        <v>0.43</v>
       </c>
       <c r="O55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.57</v>
+        <v>1.29</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -7383,19 +7389,19 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>8.969999999999999</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
@@ -7439,13 +7445,13 @@
       <c r="BL55" t="inlineStr"/>
       <c r="BM55" t="inlineStr"/>
       <c r="BN55" t="n">
-        <v>0.09478334034497266</v>
+        <v>0.2460812539987204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SO2602</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -7454,43 +7460,43 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SO1903</t>
+          <t>SO2604</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>35.2</v>
+        <v>13.7</v>
       </c>
       <c r="I56" t="n">
-        <v>61.4</v>
+        <v>71.2</v>
       </c>
       <c r="J56" t="n">
-        <v>2.6</v>
+        <v>12.8</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="L56" t="n">
-        <v>64.8</v>
+        <v>86.3</v>
       </c>
       <c r="M56" t="n">
-        <v>119.8</v>
+        <v>124.44</v>
       </c>
       <c r="N56" t="n">
-        <v>0.96</v>
+        <v>28.75</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P56" t="n">
-        <v>1.92</v>
+        <v>0.57</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -7499,19 +7505,19 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="U56" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.64</v>
+        <v>1.82</v>
       </c>
       <c r="W56" t="n">
-        <v>1.42</v>
+        <v>8.969999999999999</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
@@ -7555,13 +7561,13 @@
       <c r="BL56" t="inlineStr"/>
       <c r="BM56" t="inlineStr"/>
       <c r="BN56" t="n">
-        <v>0.5462396107845124</v>
+        <v>0.09478334034497266</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SO2603</t>
+          <t>SO2602</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -7570,43 +7576,43 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SO2001</t>
+          <t>SO1903</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>57.4</v>
+        <v>35.2</v>
       </c>
       <c r="I57" t="n">
-        <v>37.7</v>
+        <v>61.4</v>
       </c>
       <c r="J57" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="K57" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="L57" t="n">
-        <v>42.6</v>
+        <v>64.8</v>
       </c>
       <c r="M57" t="n">
-        <v>73.77</v>
+        <v>119.8</v>
       </c>
       <c r="N57" t="n">
-        <v>6.279999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4</v>
+        <v>1.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -7618,13 +7624,13 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="W57" t="n">
-        <v>5.07</v>
+        <v>1.42</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -7671,13 +7677,13 @@
       <c r="BL57" t="inlineStr"/>
       <c r="BM57" t="inlineStr"/>
       <c r="BN57" t="n">
-        <v>0.3353127879594553</v>
+        <v>0.5462396107845124</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SO2604</t>
+          <t>SO2603</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -7686,7 +7692,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SO2601</t>
+          <t>SO2001</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7695,31 +7701,31 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>26.7</v>
+        <v>57.4</v>
       </c>
       <c r="I58" t="n">
-        <v>54.8</v>
+        <v>37.7</v>
       </c>
       <c r="J58" t="n">
-        <v>16.5</v>
+        <v>2.7</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="L58" t="n">
-        <v>73.3</v>
+        <v>42.6</v>
       </c>
       <c r="M58" t="n">
-        <v>95.71000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="N58" t="n">
-        <v>37.1</v>
+        <v>6.279999999999999</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -7740,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>3.04</v>
+        <v>5.07</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -7787,13 +7793,13 @@
       <c r="BL58" t="inlineStr"/>
       <c r="BM58" t="inlineStr"/>
       <c r="BN58" t="n">
-        <v>0.1123930391308528</v>
+        <v>0.3353127879594553</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SO2605</t>
+          <t>SO2604</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -7802,7 +7808,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SO2802</t>
+          <t>SO2601</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -7811,31 +7817,31 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>16.4</v>
+        <v>26.7</v>
       </c>
       <c r="I59" t="n">
-        <v>75.40000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="J59" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>83.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="M59" t="n">
-        <v>71.12</v>
+        <v>95.71000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>5.6</v>
+        <v>37.1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -7847,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -7856,7 +7862,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.43</v>
+        <v>3.04</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -7903,13 +7909,13 @@
       <c r="BL59" t="inlineStr"/>
       <c r="BM59" t="inlineStr"/>
       <c r="BN59" t="n">
-        <v>0</v>
+        <v>0.1123930391308528</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SO2606</t>
+          <t>SO2605</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -7918,40 +7924,40 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SO2104</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>18.5</v>
+        <v>16.4</v>
       </c>
       <c r="I60" t="n">
-        <v>80.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L60" t="n">
-        <v>81.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>158.97</v>
+        <v>71.12</v>
       </c>
       <c r="N60" t="n">
-        <v>1.14</v>
+        <v>5.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.38</v>
+        <v>1.29</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -7963,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -7972,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -8019,13 +8025,13 @@
       <c r="BL60" t="inlineStr"/>
       <c r="BM60" t="inlineStr"/>
       <c r="BN60" t="n">
-        <v>0.4475268781134164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SO2801</t>
+          <t>SO2606</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -8034,61 +8040,61 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SO2502</t>
+          <t>SO2104</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+          <t>SO1202;SO1304;SO1401;SO1402;SO1403;SO1404;SO1601;SO1801;SO1802;SO1803;SO1902;SO1903;SO2103;SO2104;SO2201;SO2303;SO2307;SO2602;SO2606</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>44.1</v>
+        <v>18.5</v>
       </c>
       <c r="I61" t="n">
-        <v>36.6</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>14.6</v>
+        <v>0.7</v>
       </c>
       <c r="K61" t="n">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
       <c r="L61" t="n">
-        <v>55.9</v>
+        <v>81.5</v>
       </c>
       <c r="M61" t="n">
-        <v>81.61</v>
+        <v>158.97</v>
       </c>
       <c r="N61" t="n">
-        <v>3.57</v>
+        <v>1.14</v>
       </c>
       <c r="O61" t="n">
-        <v>10.09</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>8.140000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>7.949999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -8120,76 +8126,28 @@
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr"/>
       <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>Lower Juba</t>
-        </is>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC61" t="inlineStr">
-        <is>
-          <t>SO28</t>
-        </is>
-      </c>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="inlineStr"/>
       <c r="BD61" t="inlineStr"/>
-      <c r="BE61" t="inlineStr">
-        <is>
-          <t>Strategic developments ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>Other ---- Abduction/forced disappearance</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
-        <is>
-          <t>Military Forces of Somalia (2022-) Jubaland Intelligence and Security Agency ---- Gaaljecel Clan Militia (Somalia)</t>
-        </is>
-      </c>
-      <c r="BH61" t="inlineStr">
-        <is>
-          <t>Tuni Clan Militia (Somalia)</t>
-        </is>
-      </c>
-      <c r="BI61" t="inlineStr">
-        <is>
-          <t>Al Shabaab ---- Civilians (Somalia)</t>
-        </is>
-      </c>
-      <c r="BJ61" t="inlineStr">
-        <is>
-          <t>Abdalle Clan Group (Somalia); Women (Somalia)</t>
-        </is>
-      </c>
-      <c r="BK61" t="inlineStr">
-        <is>
-          <t>Other: On 4 March 2025, Jubaland Intelligence and Security Agency (JISA) arrested an Al Shabaab operative who was both a primary school teacher and a university student in Kismayo town (Kismaayo, Lower Juba). The militant revealed plans for abductions in town and attacks on the KDF seaport base and confirmed the existence of another Al Shabaab team, including suicide attackers, targeting government installations and public centers. ---- Around 14 July 2025 (as reported), two youths from Gaaljacel and Tuni clan militias abducted a young girl from the Abdalle clan from the Ahmed Gurey school in Midnimo village in Kismayo town (Kismaayo, Lower Juba). The girls were rescued by local police after five days. During an agreement between the Gaaljacel and Tuni and Abdalle after the incident, the Gaaljacel and Tuni clans paid an unspecified amount of money to the Abdalle clan as compensation for the sexual harassment.</t>
-        </is>
-      </c>
-      <c r="BL61" t="inlineStr">
-        <is>
-          <t>2025-03-04 ---- 2025-07-14</t>
-        </is>
-      </c>
-      <c r="BM61" t="inlineStr">
-        <is>
-          <t>Kismaayo</t>
-        </is>
-      </c>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
       <c r="BN61" t="n">
-        <v>0.3314653835237586</v>
+        <v>0.4475268781134164</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SO2802</t>
+          <t>SO2801</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -8198,7 +8156,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SO2605</t>
+          <t>SO2502</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8207,52 +8165,52 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>72.8</v>
+        <v>44.1</v>
       </c>
       <c r="I62" t="n">
-        <v>20.7</v>
+        <v>36.6</v>
       </c>
       <c r="J62" t="n">
-        <v>5.9</v>
+        <v>14.6</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="L62" t="n">
-        <v>27.2</v>
+        <v>55.9</v>
       </c>
       <c r="M62" t="n">
-        <v>71.64</v>
+        <v>81.61</v>
       </c>
       <c r="N62" t="n">
-        <v>5.5</v>
+        <v>3.57</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>10.09</v>
       </c>
       <c r="P62" t="n">
-        <v>18.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.71</v>
+        <v>1.01</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="W62" t="n">
-        <v>1.68</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -8293,7 +8251,7 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
@@ -8303,53 +8261,57 @@
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Strategic developments ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>Protest with intervention</t>
+          <t>Other ---- Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>Protesters (Somalia)</t>
+          <t>Military Forces of Somalia (2022-) Jubaland Intelligence and Security Agency ---- Gaaljecel Clan Militia (Somalia)</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>Teachers (Somalia)</t>
+          <t>Tuni Clan Militia (Somalia)</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Military Forces of Somalia (2022-) Jubaland Security Force</t>
-        </is>
-      </c>
-      <c r="BJ62" t="inlineStr"/>
+          <t>Al Shabaab ---- Civilians (Somalia)</t>
+        </is>
+      </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>Abdalle Clan Group (Somalia); Women (Somalia)</t>
+        </is>
+      </c>
       <c r="BK62" t="inlineStr">
         <is>
-          <t>On 24 May 2024, a group of protesters, including teachers, gathered in Dhobley (Afmadow, Lower Juba) against the appointment of a new district education officer. Jubaland security forces arrested primary and secondary school principals.</t>
+          <t>Other: On 4 March 2025, Jubaland Intelligence and Security Agency (JISA) arrested an Al Shabaab operative who was both a primary school teacher and a university student in Kismayo town (Kismaayo, Lower Juba). The militant revealed plans for abductions in town and attacks on the KDF seaport base and confirmed the existence of another Al Shabaab team, including suicide attackers, targeting government installations and public centers. ---- Around 14 July 2025 (as reported), two youths from Gaaljacel and Tuni clan militias abducted a young girl from the Abdalle clan from the Ahmed Gurey school in Midnimo village in Kismayo town (Kismaayo, Lower Juba). The girls were rescued by local police after five days. During an agreement between the Gaaljacel and Tuni and Abdalle after the incident, the Gaaljacel and Tuni clans paid an unspecified amount of money to the Abdalle clan as compensation for the sexual harassment.</t>
         </is>
       </c>
       <c r="BL62" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-03-04 ---- 2025-07-14</t>
         </is>
       </c>
       <c r="BM62" t="inlineStr">
         <is>
-          <t>Afmadow</t>
+          <t>Kismaayo</t>
         </is>
       </c>
       <c r="BN62" t="n">
-        <v>0.1797447056904707</v>
+        <v>0.3314653835237586</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SO2803</t>
+          <t>SO2802</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -8358,7 +8320,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SO1103</t>
+          <t>SO2605</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8367,34 +8329,34 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>56.7</v>
+        <v>72.8</v>
       </c>
       <c r="I63" t="n">
-        <v>40</v>
+        <v>20.7</v>
       </c>
       <c r="J63" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="K63" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="L63" t="n">
-        <v>43.3</v>
+        <v>27.2</v>
       </c>
       <c r="M63" t="n">
-        <v>26.67</v>
+        <v>71.64</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>18.57</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8412,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -8463,53 +8425,53 @@
       <c r="BD63" t="inlineStr"/>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Protest with intervention</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>Al Shabaab</t>
-        </is>
-      </c>
-      <c r="BH63" t="inlineStr"/>
+          <t>Protesters (Somalia)</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr">
+        <is>
+          <t>Teachers (Somalia)</t>
+        </is>
+      </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Civilians (Somalia)</t>
-        </is>
-      </c>
-      <c r="BJ63" t="inlineStr">
-        <is>
-          <t>Teachers (Somalia)</t>
-        </is>
-      </c>
+          <t>Military Forces of Somalia (2022-) Jubaland Security Force</t>
+        </is>
+      </c>
+      <c r="BJ63" t="inlineStr"/>
       <c r="BK63" t="inlineStr">
         <is>
-          <t>On 31 May 2025, Al Shabaab abducted six young men from Badhaadhe town (Badhaadhe, Lower Juba) and transferred them to Jilib, where they were subjected to physical and psychological abuse under coercion to confess to alleged affiliations with government forces. Among the detainees is a schoolteacher from Kulbiyow village, who was apprehended while traveling from Kismayo.</t>
+          <t>On 24 May 2024, a group of protesters, including teachers, gathered in Dhobley (Afmadow, Lower Juba) against the appointment of a new district education officer. Jubaland security forces arrested primary and secondary school principals.</t>
         </is>
       </c>
       <c r="BL63" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="BM63" t="inlineStr">
         <is>
-          <t>Badhaadhe</t>
+          <t>Afmadow</t>
         </is>
       </c>
       <c r="BN63" t="n">
-        <v>0</v>
+        <v>0.1797447056904707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SO2804</t>
+          <t>SO2803</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -8518,7 +8480,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SO2302</t>
+          <t>SO1103</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8527,28 +8489,28 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.4</v>
+        <v>56.7</v>
       </c>
       <c r="I64" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="J64" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="K64" t="n">
-        <v>12.2</v>
+        <v>1.7</v>
       </c>
       <c r="L64" t="n">
-        <v>97.59999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="M64" t="n">
-        <v>74.39</v>
+        <v>26.67</v>
       </c>
       <c r="N64" t="n">
-        <v>7.32</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -8572,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>12.2</v>
+        <v>1.67</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -8623,42 +8585,338 @@
       <c r="BD64" t="inlineStr"/>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>Strategic developments</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>Disrupted weapons use</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>Military Forces of Somalia (2022-) Jubaland Security Force</t>
+          <t>Al Shabaab</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr">
         <is>
+          <t>Civilians (Somalia)</t>
+        </is>
+      </c>
+      <c r="BJ64" t="inlineStr">
+        <is>
+          <t>Teachers (Somalia)</t>
+        </is>
+      </c>
+      <c r="BK64" t="inlineStr">
+        <is>
+          <t>On 31 May 2025, Al Shabaab abducted six young men from Badhaadhe town (Badhaadhe, Lower Juba) and transferred them to Jilib, where they were subjected to physical and psychological abuse under coercion to confess to alleged affiliations with government forces. Among the detainees is a schoolteacher from Kulbiyow village, who was apprehended while traveling from Kismayo.</t>
+        </is>
+      </c>
+      <c r="BL64" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="BM64" t="inlineStr">
+        <is>
+          <t>Badhaadhe</t>
+        </is>
+      </c>
+      <c r="BN64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SO2804</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SO2302</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SO1103;SO1104;SO1303;SO1502;SO1606;SO1901;SO2001;SO2002;SO2101;SO2302;SO2305;SO2401;SO2403;SO2404;SO2501;SO2502;SO2601;SO2603;SO2604;SO2605;SO2801;SO2802;SO2803;SO2804</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I65" t="n">
+        <v>78</v>
+      </c>
+      <c r="J65" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L65" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="M65" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>Lower Juba</t>
+        </is>
+      </c>
+      <c r="BA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>SO28</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>Disrupted weapons use</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>Military Forces of Somalia (2022-) Jubaland Security Force</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr">
+        <is>
           <t>Al Shabaab</t>
         </is>
       </c>
-      <c r="BJ64" t="inlineStr"/>
-      <c r="BK64" t="inlineStr">
+      <c r="BJ65" t="inlineStr"/>
+      <c r="BK65" t="inlineStr">
         <is>
           <t>Defusal: On 18 March 2024, Jubaland security forces safely defused an IED planted by suspected Al Shabaab in the perimeter wall of a Primary School in Wirkooy village (Jamaame, Lower Juba).</t>
         </is>
       </c>
-      <c r="BL64" t="inlineStr">
+      <c r="BL65" t="inlineStr">
         <is>
           <t>2024-03-18</t>
         </is>
       </c>
-      <c r="BM64" t="inlineStr">
+      <c r="BM65" t="inlineStr">
         <is>
           <t>Jamaame</t>
         </is>
       </c>
-      <c r="BN64" t="n">
+      <c r="BN65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>October 2024: An educator was shot and killed by suspected Al Shabaab militants.</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>Al-Shabaab</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr"/>
+      <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="inlineStr"/>
+      <c r="BM66" t="inlineStr"/>
+      <c r="BN66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8929,13 +9187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B8869E-561B-4D7B-B5CF-663EEBECC15F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{623584BF-C9DA-4EB9-B1CC-5AD19B317BCD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9BFDFA4-5A80-458D-A2FE-FA44B5F171B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D4B7A2-A8C6-49DC-B762-333256DB09BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21CFC321-ADC6-466C-AA54-D23B7F6A64AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{713F52B6-97B2-4DA4-97FA-0C06BCFC8D37}"/>
 </file>